--- a/data/raw/mission_40671_20220201_20220228.xlsx
+++ b/data/raw/mission_40671_20220201_20220228.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" r:id="Re4ca61ecef57449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" r:id="R475d1c678af64321"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/data/raw/mission_40671_20220201_20220228.xlsx
+++ b/data/raw/mission_40671_20220201_20220228.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" r:id="R475d1c678af64321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" r:id="Rea155df1868341d7"/>
   </x:sheets>
 </x:workbook>
 </file>
